--- a/internal_doc/05.测试设计/参数校验/集群管理参数校验列表.xlsx
+++ b/internal_doc/05.测试设计/参数校验/集群管理参数校验列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="7830" yWindow="270" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,10 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="78">
-  <si>
-    <t>参数名</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="74">
   <si>
     <t>参数项</t>
   </si>
@@ -34,58 +31,7 @@
   </si>
   <si>
     <r>
-      <t>集群名（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>OM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>界面）</t>
-    </r>
-  </si>
-  <si>
-    <t>集群名</t>
-  </si>
-  <si>
-    <r>
-      <t>只能由数字字母下划线组成，并且长度在</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>1-255</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>个字符内，必填</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1、</t>
+      <t>2、</t>
     </r>
     <r>
       <rPr>
@@ -104,177 +50,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>数字</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>字母</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>下划线，如</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>cluster</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>2、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>长度分别为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>1,255</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>带有特殊字符，如￥</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>#%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>2、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
       <t>为空</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>3、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>长度为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>256</t>
     </r>
   </si>
   <si>
@@ -1554,6 +1330,22 @@
   </si>
   <si>
     <t>备注</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>组管理</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点管理</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>子特性名称</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试点</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1618,7 +1410,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1628,6 +1420,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1659,7 +1457,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1667,9 +1465,6 @@
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
@@ -1682,12 +1477,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2050,643 +1852,615 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="20.875" customWidth="1"/>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="32.375" customWidth="1"/>
-    <col min="4" max="4" width="22.125" customWidth="1"/>
-    <col min="5" max="5" width="31.875" customWidth="1"/>
+    <col min="2" max="2" width="20.875" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="32.375" customWidth="1"/>
+    <col min="5" max="5" width="22.125" customWidth="1"/>
+    <col min="6" max="6" width="31.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:13" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" s="13" customFormat="1">
+      <c r="A2" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="B4" s="11"/>
+      <c r="C4" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="B6" s="11"/>
+      <c r="C6" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="B9" s="11"/>
+      <c r="C9" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="27">
-      <c r="A2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="5" t="s">
+      <c r="F10" s="11"/>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="B11" s="11"/>
+      <c r="C11" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="B12" s="11"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="11"/>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="B13" s="5"/>
+      <c r="C13" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="B14" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="B15" s="11"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="B16" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" ht="27">
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" s="11"/>
+      <c r="F17" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="11"/>
+      <c r="F18" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D19" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E19" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F19" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="6" t="s">
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="B21" s="11"/>
+      <c r="C21" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="B23" s="11"/>
+      <c r="C23" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="B26" s="11"/>
+      <c r="C26" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F27" s="11"/>
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="B28" s="11"/>
+      <c r="C28" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="B29" s="11"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F29" s="11"/>
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="B30" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="G30" s="2"/>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E31" s="11"/>
+      <c r="F31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" s="2"/>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E32" s="11"/>
+      <c r="F32" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G32" s="2"/>
+    </row>
+    <row r="33" spans="2:7">
+      <c r="B33" s="11"/>
+      <c r="C33" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="8" t="s">
+      <c r="D33" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="E33" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="F33" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="8" t="s">
+      <c r="G33" s="2"/>
+    </row>
+    <row r="34" spans="2:7">
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E34" s="11"/>
+      <c r="F34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" s="2"/>
+    </row>
+    <row r="35" spans="2:7">
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="E35" s="11"/>
+      <c r="F35" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="G35" s="2"/>
+    </row>
+    <row r="36" spans="2:7" ht="27">
+      <c r="B36" s="11"/>
+      <c r="C36" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="6" t="s">
+      <c r="D36" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="G36" s="2"/>
+    </row>
+    <row r="37" spans="2:7">
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F37" s="10"/>
+      <c r="G37" s="2"/>
+    </row>
+    <row r="38" spans="2:7">
+      <c r="B38" s="11"/>
+      <c r="C38" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="8"/>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="8"/>
-      <c r="B14" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="8"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6"/>
-      <c r="B16" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F17" s="2"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="8"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="F18" s="2"/>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="F19" s="2"/>
-    </row>
-    <row r="20" spans="1:6" ht="27">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D20" s="8"/>
-      <c r="E20" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="F20" s="2"/>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" s="8"/>
-      <c r="E21" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="F21" s="2"/>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F22" s="2"/>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F23" s="2"/>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F24" s="2"/>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F25" s="2"/>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F26" s="2"/>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F27" s="2"/>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F28" s="2"/>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F29" s="2"/>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" s="8"/>
-      <c r="F30" s="2"/>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="8"/>
-      <c r="B31" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F31" s="2"/>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="8"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E32" s="8"/>
-      <c r="F32" s="2"/>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F33" s="2"/>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="8"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D34" s="8"/>
-      <c r="E34" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F34" s="2"/>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="D35" s="8"/>
-      <c r="E35" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="F35" s="2"/>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C36" s="11" t="s">
+      <c r="D38" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D36" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F36" s="2"/>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="8"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="11" t="s">
+      <c r="E38" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D37" s="8"/>
-      <c r="E37" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F37" s="2"/>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="8"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="11" t="s">
+      <c r="F38" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="G38" s="2"/>
+    </row>
+    <row r="39" spans="2:7">
+      <c r="B39" s="11"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D38" s="8"/>
-      <c r="E38" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="F38" s="2"/>
-    </row>
-    <row r="39" spans="1:6" ht="27">
-      <c r="A39" s="8"/>
-      <c r="B39" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F39" s="2"/>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="8"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E40" s="5"/>
-      <c r="F40" s="2"/>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="8"/>
-      <c r="B41" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F41" s="2"/>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="8"/>
-      <c r="B42" s="5"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="E42" s="8"/>
-      <c r="F42" s="2"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="57">
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="A5:A13"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="A14:A15"/>
+  <mergeCells count="54">
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="B30:B37"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="E30:E32"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="E33:E35"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="D23:D25"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="F11:F12"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
     <mergeCell ref="E14:E15"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="B26:B28"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="A33:A40"/>
-    <mergeCell ref="B33:B35"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="B2:B10"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/05.测试设计/参数校验/集群管理参数校验列表.xlsx
+++ b/internal_doc/05.测试设计/参数校验/集群管理参数校验列表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="118">
   <si>
     <t>参数项</t>
   </si>
@@ -797,23 +797,41 @@
     <t>CreateNode</t>
   </si>
   <si>
-    <r>
-      <t>字符串</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，必填</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>3、</t>
+    <t>RemoveNode</t>
+  </si>
+  <si>
+    <r>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、和实际端口不一致</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Json</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>对象</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1、</t>
     </r>
     <r>
       <rPr>
@@ -828,11 +846,453 @@
       <rPr>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>字符串类型，如</t>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Json</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>对象，如</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>logsize</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>64</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>默认为空</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2-3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个必填项</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、全配</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个参数（已覆盖）、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个参数</t>
+    </r>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>组管理</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点管理</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>子特性名称</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试点</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、字符串类型，必填</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、正确的主机</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>IP</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、正确的主机名</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、不可用的主机名、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>IP</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、可用端口号，如</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>11830</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>11830</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>”</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、为空</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、端口号冲突</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、string类型，必填</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、字符串类型，必填</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、和其他节点路径不冲突</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>已存在的目录</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>如</t>
     </r>
     <r>
       <rPr>
@@ -843,10 +1303,132 @@
       </rPr>
       <t>/opt</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <t>4、</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、不带路径标记”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>如</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>opt</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、为空</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、路径有冲突，为其他节点目录</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、路径没有权限</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
     </r>
     <r>
       <rPr>
@@ -855,6 +1437,45 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不存在的目录</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库配置中涉及所有参数</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
       <t xml:space="preserve">  </t>
     </r>
     <r>
@@ -865,15 +1486,87 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>文件路径</t>
-    </r>
-  </si>
-  <si>
-    <t>RemoveNode</t>
-  </si>
-  <si>
-    <r>
-      <t>1、</t>
+      <t>为空</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、数据库配置中包含的所有参数</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、实际存在的节点主机名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>/IP</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、和实际节点不一致：主机名、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>IP,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>如同组内其他节点信息、其他组节点信息</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
     </r>
     <r>
       <rPr>
@@ -892,12 +1585,105 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>为字符串类型</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>2、</t>
+      <t>为字符串类型，必填</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、非</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>IP/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>主机名格式，如</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>test</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>￥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>%#</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>192.ttest</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
     </r>
     <r>
       <rPr>
@@ -916,17 +1702,28 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>必填</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>3、</t>
+      <t>和存在节点信息一致</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
     </r>
     <r>
       <rPr>
         <sz val="7"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
@@ -935,13 +1732,39 @@
     <r>
       <rPr>
         <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>和存在节点信息一致</t>
-    </r>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>为字符串类型，必填</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、实际存在端口号，如</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>11800</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -952,249 +1775,531 @@
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、和存在节点</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>host</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>不一致</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1、</t>
+        <family val="2"/>
+      </rPr>
+      <t>、非整数值，如</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>test</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、非整数值，如</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>abc1</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、非</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>json</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>对象</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、和实际配置值不一致</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>attachNode</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、string类型，必填</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、和实际节点信息一致</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、和实际节点服务名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>端口一致</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、实际存在的服务名</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>、非整数值，如</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>test</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
     </r>
     <r>
       <rPr>
         <i/>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>和实际节点服务名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>端口一致</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>options</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Json</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>对象</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>2、和实际信息一致</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Json</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>对象，实际存在值</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、默认为空</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、和实际配置值不一致</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、非</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>json</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>对象</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>KeepData</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、bool类型，默认值为false</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="7"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>字符串</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>2、</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="7"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>必填</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>3、</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="7"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>和实际端口一致</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、和实际端口不一致</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Json</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>对象</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Json</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>对象，如</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>logsize</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>64</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>2、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>默认为空</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>非</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>json</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>对象</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>2-3</t>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>为空</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、设置参数值：true、false</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、目标节点不属于当前组，切勿设置为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>true</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、非</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>bool</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>类型，如“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>true”</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、目标节点原本不属于当前组，设置参数值为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>true</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2-4</t>
     </r>
     <r>
       <rPr>
@@ -1206,6 +2311,7 @@
       </rPr>
       <t>个</t>
     </r>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1240,40 +2346,7 @@
       </rPr>
       <t>个必填项</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、全配</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>个</t>
-    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1315,7 +2388,7 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>4</t>
+      <t>5</t>
     </r>
     <r>
       <rPr>
@@ -1327,33 +2400,18 @@
       </rPr>
       <t>个参数</t>
     </r>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>组管理</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>节点管理</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>子特性名称</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试点</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>detachNode</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1389,25 +2447,86 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="10.5"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="7"/>
-      <color rgb="FFFF0000"/>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="宋体"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1430,7 +2549,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1453,11 +2572,74 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="9" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="9" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1477,9 +2659,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
@@ -1489,7 +2672,52 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1852,22 +3080,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="20.875" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="32.375" customWidth="1"/>
-    <col min="5" max="5" width="22.125" customWidth="1"/>
+    <col min="5" max="5" width="29.25" customWidth="1"/>
     <col min="6" max="6" width="31.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
@@ -1882,23 +3110,23 @@
         <v>3</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" s="13" customFormat="1">
-      <c r="A2" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" s="10" customFormat="1">
+      <c r="A2" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="12" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="7" t="s">
@@ -1913,24 +3141,24 @@
       <c r="M2" s="7"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="11"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="12"/>
       <c r="F3" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G3" s="2"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="B4" s="11"/>
-      <c r="C4" s="11" t="s">
+      <c r="B4" s="12"/>
+      <c r="C4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="12" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="5" t="s">
@@ -1939,21 +3167,21 @@
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:13">
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="11"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="12"/>
       <c r="F5" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:13">
-      <c r="B6" s="11"/>
-      <c r="C6" s="11" t="s">
+      <c r="B6" s="12"/>
+      <c r="C6" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="11" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="5" t="s">
@@ -1965,9 +3193,9 @@
       <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:13">
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="10"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="11"/>
       <c r="E7" s="5" t="s">
         <v>17</v>
       </c>
@@ -1977,9 +3205,9 @@
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="10"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="11"/>
       <c r="E8" s="6"/>
       <c r="F8" s="5" t="s">
         <v>20</v>
@@ -1987,465 +3215,830 @@
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="B9" s="11"/>
-      <c r="C9" s="11" t="s">
+      <c r="B9" s="12"/>
+      <c r="C9" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="12" t="s">
         <v>22</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="12" t="s">
         <v>24</v>
       </c>
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
       <c r="E10" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="11"/>
+      <c r="F10" s="12"/>
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:13">
-      <c r="B11" s="11"/>
-      <c r="C11" s="10" t="s">
+      <c r="B11" s="12"/>
+      <c r="C11" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="12" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="12" t="s">
         <v>29</v>
       </c>
       <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="B12" s="11"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="12"/>
       <c r="E12" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="11"/>
+      <c r="F12" s="12"/>
       <c r="G12" s="2"/>
     </row>
-    <row r="13" spans="1:13">
-      <c r="B13" s="5"/>
-      <c r="C13" s="8" t="s">
+    <row r="13" spans="1:13" s="16" customFormat="1">
+      <c r="B13" s="17"/>
+      <c r="C13" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="G13" s="2"/>
+      <c r="G13" s="19"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="B15" s="11"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="5" t="s">
+      <c r="G14" s="15"/>
+    </row>
+    <row r="15" spans="1:13" s="16" customFormat="1">
+      <c r="B15" s="23"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="G15" s="2"/>
+      <c r="G15" s="19"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="G16" s="2"/>
+      <c r="G16" s="15"/>
     </row>
     <row r="17" spans="1:7" ht="27">
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
       <c r="D17" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E17" s="11"/>
+      <c r="E17" s="9"/>
       <c r="F17" s="5" t="s">
         <v>46</v>
       </c>
       <c r="G17" s="2"/>
     </row>
-    <row r="18" spans="1:7">
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="5" t="s">
+    <row r="18" spans="1:7" s="16" customFormat="1">
+      <c r="B18" s="23"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="11"/>
-      <c r="F18" s="5" t="s">
+      <c r="E18" s="17"/>
+      <c r="F18" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" s="11" t="s">
+      <c r="G18" s="19"/>
+    </row>
+    <row r="19" spans="1:7" ht="27">
+      <c r="A19" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G19" s="2"/>
+      <c r="D19" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="G19" s="15"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="11"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="9" t="s">
+        <v>65</v>
+      </c>
       <c r="F20" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G20" s="2"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="B21" s="11"/>
-      <c r="C21" s="11" t="s">
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="1:7" ht="27">
+      <c r="B22" s="12"/>
+      <c r="C22" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D22" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="B25" s="12"/>
+      <c r="C25" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" spans="1:7" ht="25.5">
+      <c r="B29" s="12"/>
+      <c r="C29" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E29" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G29" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="F30" s="9"/>
+      <c r="G30" s="2"/>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="B31" s="12"/>
+      <c r="C31" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G31" s="2"/>
+    </row>
+    <row r="32" spans="1:7" s="16" customFormat="1">
+      <c r="B32" s="23"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="F32" s="17"/>
+      <c r="G32" s="19"/>
+    </row>
+    <row r="33" spans="2:7" ht="27">
+      <c r="B33" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="E21" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="5" t="s">
+      <c r="C33" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="G33" s="15"/>
+    </row>
+    <row r="34" spans="2:7">
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G34" s="2"/>
+    </row>
+    <row r="35" spans="2:7">
+      <c r="B35" s="12"/>
+      <c r="C35" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="G35" s="2"/>
+    </row>
+    <row r="36" spans="2:7">
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="E36" s="9"/>
+      <c r="F36" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="B23" s="11"/>
-      <c r="C23" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" s="5" t="s">
+      <c r="G36" s="2"/>
+    </row>
+    <row r="37" spans="2:7">
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F23" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="5" t="s">
+      <c r="G37" s="2"/>
+    </row>
+    <row r="38" spans="2:7">
+      <c r="B38" s="12"/>
+      <c r="C38" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D38" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="F24" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="B26" s="11"/>
-      <c r="C26" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F26" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F27" s="11"/>
-      <c r="G27" s="2"/>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="B28" s="11"/>
-      <c r="C28" s="10" t="s">
+      <c r="E38" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="G38" s="2"/>
+    </row>
+    <row r="39" spans="2:7">
+      <c r="B39" s="12"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="G39" s="2"/>
+    </row>
+    <row r="40" spans="2:7">
+      <c r="B40" s="12"/>
+      <c r="C40" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D28" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F28" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G28" s="2"/>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="B29" s="11"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="5" t="s">
+      <c r="D40" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="G40" s="2"/>
+    </row>
+    <row r="41" spans="2:7" s="16" customFormat="1">
+      <c r="B41" s="23"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="F41" s="23"/>
+      <c r="G41" s="19"/>
+    </row>
+    <row r="42" spans="2:7" ht="27">
+      <c r="B42" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="C42" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D42" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="F42" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="G42" s="15"/>
+    </row>
+    <row r="43" spans="2:7">
+      <c r="B43" s="12"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" s="2"/>
+    </row>
+    <row r="44" spans="2:7">
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="G44" s="2"/>
+    </row>
+    <row r="45" spans="2:7" ht="26.25">
+      <c r="B45" s="12"/>
+      <c r="C45" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G45" s="2"/>
+    </row>
+    <row r="46" spans="2:7">
+      <c r="B46" s="12"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G46" s="2"/>
+    </row>
+    <row r="47" spans="2:7">
+      <c r="B47" s="12"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="G47" s="2"/>
+    </row>
+    <row r="48" spans="2:7">
+      <c r="B48" s="12"/>
+      <c r="C48" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="G48" s="2"/>
+    </row>
+    <row r="49" spans="2:7">
+      <c r="B49" s="12"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="G49" s="2"/>
+    </row>
+    <row r="50" spans="2:7">
+      <c r="B50" s="12"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E50" s="6"/>
+      <c r="F50" s="9"/>
+      <c r="G50" s="2"/>
+    </row>
+    <row r="51" spans="2:7">
+      <c r="B51" s="12"/>
+      <c r="C51" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D51" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="E51" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="G51" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7" ht="27">
+      <c r="B52" s="12"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="E52" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="G52" s="2"/>
+    </row>
+    <row r="53" spans="2:7">
+      <c r="B53" s="12"/>
+      <c r="C53" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="G53" s="2"/>
+    </row>
+    <row r="54" spans="2:7" s="16" customFormat="1">
+      <c r="B54" s="23"/>
+      <c r="C54" s="25"/>
+      <c r="D54" s="23"/>
+      <c r="E54" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="F29" s="11"/>
-      <c r="G29" s="2"/>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="B30" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="C30" s="11" t="s">
+      <c r="F54" s="17"/>
+      <c r="G54" s="19"/>
+    </row>
+    <row r="55" spans="2:7" ht="27">
+      <c r="B55" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C55" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G30" s="2"/>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E31" s="11"/>
-      <c r="F31" s="5" t="s">
+      <c r="D55" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E55" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="F55" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="G55" s="15"/>
+    </row>
+    <row r="56" spans="2:7">
+      <c r="B56" s="12"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E56" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F56" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G31" s="2"/>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E32" s="11"/>
-      <c r="F32" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G32" s="2"/>
-    </row>
-    <row r="33" spans="2:7">
-      <c r="B33" s="11"/>
-      <c r="C33" s="11" t="s">
+      <c r="G56" s="2"/>
+    </row>
+    <row r="57" spans="2:7">
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="8"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="G57" s="2"/>
+    </row>
+    <row r="58" spans="2:7" ht="26.25">
+      <c r="B58" s="12"/>
+      <c r="C58" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D33" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G33" s="2"/>
-    </row>
-    <row r="34" spans="2:7">
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="E34" s="11"/>
-      <c r="F34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G34" s="2"/>
-    </row>
-    <row r="35" spans="2:7">
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="E35" s="11"/>
-      <c r="F35" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="G35" s="2"/>
-    </row>
-    <row r="36" spans="2:7" ht="27">
-      <c r="B36" s="11"/>
-      <c r="C36" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F36" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="G36" s="2"/>
-    </row>
-    <row r="37" spans="2:7">
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F37" s="10"/>
-      <c r="G37" s="2"/>
-    </row>
-    <row r="38" spans="2:7">
-      <c r="B38" s="11"/>
-      <c r="C38" s="10" t="s">
+      <c r="D58" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E58" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G58" s="2"/>
+    </row>
+    <row r="59" spans="2:7">
+      <c r="B59" s="12"/>
+      <c r="C59" s="12"/>
+      <c r="D59" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="E59" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G59" s="2"/>
+    </row>
+    <row r="60" spans="2:7">
+      <c r="B60" s="12"/>
+      <c r="C60" s="12"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="9"/>
+      <c r="F60" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="G60" s="2"/>
+    </row>
+    <row r="61" spans="2:7">
+      <c r="B61" s="12"/>
+      <c r="C61" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="G61" s="2"/>
+    </row>
+    <row r="62" spans="2:7">
+      <c r="B62" s="12"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="G62" s="2"/>
+    </row>
+    <row r="63" spans="2:7">
+      <c r="B63" s="12"/>
+      <c r="C63" s="12"/>
+      <c r="D63" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E63" s="6"/>
+      <c r="F63" s="9"/>
+      <c r="G63" s="2"/>
+    </row>
+    <row r="64" spans="2:7">
+      <c r="B64" s="12"/>
+      <c r="C64" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D64" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="E64" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="G64" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7" ht="27">
+      <c r="B65" s="12"/>
+      <c r="C65" s="12"/>
+      <c r="D65" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="E65" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="G65" s="2"/>
+    </row>
+    <row r="66" spans="2:7">
+      <c r="B66" s="12"/>
+      <c r="C66" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D38" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F38" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="G38" s="2"/>
-    </row>
-    <row r="39" spans="2:7">
-      <c r="B39" s="11"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F39" s="11"/>
-      <c r="G39" s="2"/>
+      <c r="D66" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="E66" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="G66" s="2"/>
+    </row>
+    <row r="67" spans="2:7" s="16" customFormat="1">
+      <c r="B67" s="23"/>
+      <c r="C67" s="25"/>
+      <c r="D67" s="23"/>
+      <c r="E67" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="F67" s="17"/>
+      <c r="G67" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="54">
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="B30:B37"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="E30:E32"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="E33:E35"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="D23:D25"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="F11:F12"/>
+  <mergeCells count="69">
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="C58:C60"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="C61:C63"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="D53:D54"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="C48:C50"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="C45:C47"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="C14:C15"/>
     <mergeCell ref="D14:D15"/>
@@ -2461,9 +4054,40 @@
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="D9:D10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="B33:B39"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="C35:C37"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
   </mergeCells>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2472,7 +4096,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <sheetData/>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2482,7 +4106,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <sheetData/>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>